--- a/data/merged/2026-10-08/MERGED_FR_Wet-Dry-Floor-Washer_2026-10-08.xlsx
+++ b/data/merged/2026-10-08/MERGED_FR_Wet-Dry-Floor-Washer_2026-10-08.xlsx
@@ -1008,7 +1008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR4"/>
+  <dimension ref="A1:BR3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -1812,204 +1812,6 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
-        <v>3</v>
-      </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>B0H69GTK93</t>
-        </is>
-      </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="G4" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Generic</t>
-        </is>
-      </c>
-      <c r="H4" s="14" t="inlineStr">
-        <is>
-          <t>Aspirateur sans Fil 50000Pa 600W 60Min Autonomie Grand Bac À Poussière Filtration 8 Étages pour Maison Poils Animaux</t>
-        </is>
-      </c>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/dp/B0H69GTK93?psc=1</t>
-        </is>
-      </c>
-      <c r="K4" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/710l9PXoMvL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L4" s="14" t="inlineStr">
-        <is>
-          <t>B0H69GTK93</t>
-        </is>
-      </c>
-      <c r="M4" s="14" t="inlineStr">
-        <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs eau et poussière à usage domestique</t>
-        </is>
-      </c>
-      <c r="N4" s="14" t="inlineStr">
-        <is>
-          <t>Voir les 100 premiers en Cuisine et Maison</t>
-        </is>
-      </c>
-      <c r="O4" s="15">
-        <v>621749</v>
-      </c>
-      <c r="P4" s="15">
-        <v>-18457</v>
-      </c>
-      <c r="Q4" s="16">
-        <v>-0.03</v>
-      </c>
-      <c r="R4" s="17" t="inlineStr">
-        <is>
-          <t>Aspirateurs eau et poussière à usage domestique</t>
-        </is>
-      </c>
-      <c r="S4" s="18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T4" s="15"/>
-      <c r="U4" s="16">
-        <v>-0.81</v>
-      </c>
-      <c r="V4" s="15"/>
-      <c r="W4" s="15"/>
-      <c r="X4" s="15"/>
-      <c r="Y4" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="20">
-        <v>39.99</v>
-      </c>
-      <c r="AA4"/>
-      <c r="AB4"/>
-      <c r="AC4" s="2"/>
-      <c r="AD4" s="19">
-        <v>1</v>
-      </c>
-      <c r="AE4" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="21">
-        <v>4</v>
-      </c>
-      <c r="AG4" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="20">
-        <v>8.44</v>
-      </c>
-      <c r="AI4" s="16">
-        <v>0.64</v>
-      </c>
-      <c r="AJ4"/>
-      <c r="AK4" s="13" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="AL4" s="19">
-        <v>88</v>
-      </c>
-      <c r="AM4" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN4" s="13"/>
-      <c r="AO4" s="13"/>
-      <c r="AP4"/>
-      <c r="AQ4" s="19"/>
-      <c r="AR4" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS4" s="14" t="inlineStr">
-        <is>
-          <t>CHENMW Department Store</t>
-        </is>
-      </c>
-      <c r="AT4" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU4" s="13"/>
-      <c r="AV4" s="14"/>
-      <c r="AW4" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AQBFEG6BI2O00</t>
-        </is>
-      </c>
-      <c r="AX4" s="13"/>
-      <c r="AY4" s="13"/>
-      <c r="AZ4" s="13"/>
-      <c r="BA4" s="13"/>
-      <c r="BB4" s="13"/>
-      <c r="BC4" s="13"/>
-      <c r="BD4" s="13"/>
-      <c r="BE4" s="13"/>
-      <c r="BF4" s="13"/>
-      <c r="BG4" s="13"/>
-      <c r="BH4" s="14"/>
-      <c r="BI4"/>
-      <c r="BJ4" s="23" t="inlineStr">
-        <is>
-          <t>4,46 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK4" s="23" t="inlineStr">
-        <is>
-          <t>4.46 kg</t>
-        </is>
-      </c>
-      <c r="BL4" s="23" t="inlineStr">
-        <is>
-          <t>12L x 7l x 18H centimètres</t>
-        </is>
-      </c>
-      <c r="BM4" s="23"/>
-      <c r="BN4" s="23" t="inlineStr">
-        <is>
-          <t>4.46 kg</t>
-        </is>
-      </c>
-      <c r="BO4" s="23" t="inlineStr">
-        <is>
-          <t>4.46 kg</t>
-        </is>
-      </c>
-      <c r="BP4" s="23" t="inlineStr">
-        <is>
-          <t>44.5 x 33.6 x 19.5 cm</t>
-        </is>
-      </c>
-      <c r="BQ4" s="23" t="inlineStr">
-        <is>
-          <t>44.50 x 33.60 x 19.50 cm</t>
-        </is>
-      </c>
-      <c r="BR4" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2029,19 +1831,82 @@
     <hyperlink ref="L3" r:id="rId13" tooltip="https://www.amazon.fr/dp/B0GL7P6391"/>
     <hyperlink ref="M3" r:id="rId14" tooltip="https://www.amazon.fr/b?node=218877814031"/>
     <hyperlink ref="N3" r:id="rId15"/>
-    <hyperlink ref="C4" r:id="rId16" tooltip="https://www.amazon.fr/dp/B0H69GTK93"/>
-    <hyperlink ref="G4" r:id="rId17" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Generic"/>
-    <hyperlink ref="J4" r:id="rId18" tooltip="https://www.amazon.fr/dp/B0H69GTK93?psc=1"/>
-    <hyperlink ref="K4" r:id="rId19" tooltip="https://images-na.ssl-images-amazon.com/images/I/710l9PXoMvL._AC_US600_.jpg"/>
-    <hyperlink ref="L4" r:id="rId20" tooltip="https://www.amazon.fr/dp/B0H69GTK93"/>
-    <hyperlink ref="M4" r:id="rId21" tooltip="https://www.amazon.fr/b?node=218877814031"/>
-    <hyperlink ref="N4" r:id="rId22"/>
-    <hyperlink ref="AW4" r:id="rId23" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AQBFEG6BI2O00"/>
   </hyperlinks>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" style="1" customWidth="1"/>
+    <col min="2" max="5" width="13" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10" style="4" customWidth="1"/>
+    <col min="7" max="7" width="10" style="6" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>品牌</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>月销量</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>月销售额(€)</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>近1年销量</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>近一年销售额(€)</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>平均价格(€)</t>
+        </is>
+      </c>
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>市场份额</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>JONR</t>
+        </is>
+      </c>
+      <c r="B2" s="15">
+        <v>0</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0</v>
+      </c>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="22"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -2055,7 +1920,7 @@
     <row r="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>品牌</t>
+          <t>卖家</t>
         </is>
       </c>
       <c r="B1" s="8" t="inlineStr">
@@ -2092,7 +1957,7 @@
     <row r="2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Generic</t>
+          <t>JONR Official</t>
         </is>
       </c>
       <c r="B2" s="15">
@@ -2109,7 +1974,7 @@
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>JONR</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B3" s="15">
@@ -2122,111 +1987,6 @@
       <c r="E3" s="15"/>
       <c r="F3" s="20"/>
       <c r="G3" s="22"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="25" style="1" customWidth="1"/>
-    <col min="2" max="5" width="13" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10" style="4" customWidth="1"/>
-    <col min="7" max="7" width="10" style="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>卖家</t>
-        </is>
-      </c>
-      <c r="B1" s="8" t="inlineStr">
-        <is>
-          <t>月销量</t>
-        </is>
-      </c>
-      <c r="C1" s="8" t="inlineStr">
-        <is>
-          <t>月销售额(€)</t>
-        </is>
-      </c>
-      <c r="D1" s="8" t="inlineStr">
-        <is>
-          <t>近1年销量</t>
-        </is>
-      </c>
-      <c r="E1" s="8" t="inlineStr">
-        <is>
-          <t>近一年销售额(€)</t>
-        </is>
-      </c>
-      <c r="F1" s="10" t="inlineStr">
-        <is>
-          <t>平均价格(€)</t>
-        </is>
-      </c>
-      <c r="G1" s="12" t="inlineStr">
-        <is>
-          <t>市场份额</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>CHENMW Department Store</t>
-        </is>
-      </c>
-      <c r="B2" s="15">
-        <v>0</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0</v>
-      </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="22"/>
-    </row>
-    <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>JONR Official</t>
-        </is>
-      </c>
-      <c r="B3" s="15">
-        <v>0</v>
-      </c>
-      <c r="C3" s="15">
-        <v>0</v>
-      </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="22"/>
-    </row>
-    <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B4" s="15">
-        <v>0</v>
-      </c>
-      <c r="C4" s="15">
-        <v>0</v>
-      </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
